--- a/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt2_rubricas.xlsx
@@ -1608,13 +1608,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA322BE1-9CDA-4FD5-B4D5-D28A76E04C48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2E2FA8-D2FA-4809-83AE-493AEEB26447}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A03347A-7095-47A9-A487-5C194B6FB671}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55554E94-A6DB-42C0-BDCC-A12904484400}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CFA0FB6-1E30-4A90-88CF-F01237BB59D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{435E3771-52E0-4C4E-94B0-7605BC077CD8}"/>
 </file>